--- a/outputs/daily/hr_rankings_2026-08-09_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-09_full.xlsx
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Last 7 games: 2/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>56.2</v>
+        <v>54.4</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -12739,32 +12739,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>678545</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Osleivis Basabe</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-09T20:05:00Z</t>
+          <t>2026-08-09T18:10:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -12774,21 +12774,21 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Troy Melton</t>
+          <t>Connor Prielipp</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>675512</t>
+          <t>687570</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>56.4</v>
+        <v>56.8</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12806,13 +12806,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>62.3</v>
+        <v>61</v>
       </c>
       <c r="Q45" t="n">
-        <v>30.1</v>
+        <v>42.3</v>
       </c>
       <c r="R45" t="n">
-        <v>52.3</v>
+        <v>37.6</v>
       </c>
       <c r="S45" t="n">
         <v>86.40000000000001</v>
@@ -12821,7 +12821,7 @@
         <v>50</v>
       </c>
       <c r="U45" t="n">
-        <v>85</v>
+        <v>84.7</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -12893,122 +12893,122 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 7.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>51.13</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>101.4357</t>
+          <t>103.2722</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>0.4696</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>0.2195</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.3624</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>76.71</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>0.2088</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>0.3528</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>0.1379</t>
+          <t>0.159</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>24.77</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr"/>
@@ -13019,47 +13019,47 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>802139</t>
+          <t>678545</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JJ Wetherholt</t>
+          <t>Osleivis Basabe</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-09T18:15:00Z</t>
+          <t>2026-08-09T20:05:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Troy Melton</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>675512</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -13068,7 +13068,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>56.1</v>
+        <v>56.4</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -13082,26 +13082,26 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>37.8</v>
+        <v>62.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>54.4</v>
+        <v>30.1</v>
       </c>
       <c r="R46" t="n">
-        <v>68.09999999999999</v>
+        <v>52.3</v>
       </c>
       <c r="S46" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T46" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U46" t="n">
-        <v>2.5</v>
+        <v>85</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -13153,142 +13153,142 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 7.7 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>99.317</t>
+          <t>101.4357</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.526</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.233</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.349</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.371</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>90.56</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>0.4713</t>
+          <t>0.3528</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>0.1847</t>
+          <t>0.1379</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -13299,56 +13299,56 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>545341</t>
+          <t>802139</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>JJ Wetherholt</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-09T18:10:00Z</t>
+          <t>2026-08-09T18:15:00Z</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -13362,26 +13362,26 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>51.2</v>
+        <v>37.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>37.5</v>
+        <v>54.4</v>
       </c>
       <c r="R47" t="n">
-        <v>57.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S47" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T47" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U47" t="n">
-        <v>24.9</v>
+        <v>2.5</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -13416,7 +13416,7 @@
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr"/>
@@ -13433,12 +13433,12 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -13448,12 +13448,12 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/14, 0 HR</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 13.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.4 HR allowed</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
@@ -13463,112 +13463,112 @@
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>11.14</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>48.52</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>102.9638</t>
+          <t>99.317</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>0.4731</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>0.1998</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>0.3344</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>42.54</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>0.2262</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.56</t>
         </is>
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>0.3735</t>
+          <t>0.4713</t>
         </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>0.1424</t>
+          <t>0.1847</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr"/>
@@ -13579,47 +13579,47 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>545341</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Julio Rodríguez</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-09T20:10:00Z</t>
+          <t>2026-08-09T18:10:00Z</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Delayed</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -13642,26 +13642,26 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>46.6</v>
+        <v>51.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>40.5</v>
+        <v>37.5</v>
       </c>
       <c r="R48" t="n">
-        <v>52.4</v>
+        <v>57.1</v>
       </c>
       <c r="S48" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T48" t="n">
         <v>78</v>
       </c>
       <c r="U48" t="n">
-        <v>78.7</v>
+        <v>24.9</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -13713,142 +13713,142 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/14, 0 HR</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 10.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>11.14</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>48.52</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>102.7754</t>
+          <t>102.9638</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>0.4748</t>
+          <t>0.4731</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>0.1985</t>
+          <t>0.1998</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>0.3496</t>
+          <t>0.3344</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>66.99</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>0.2262</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>0.3802</t>
+          <t>0.3735</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.1424</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr"/>
@@ -13859,56 +13859,56 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-09T18:10:00Z</t>
+          <t>2026-08-09T20:10:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13922,26 +13922,26 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>40</v>
+        <v>46.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>44.2</v>
+        <v>40.5</v>
       </c>
       <c r="R49" t="n">
-        <v>57.1</v>
+        <v>52.4</v>
       </c>
       <c r="S49" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T49" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U49" t="n">
-        <v>60.3</v>
+        <v>78.7</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -14003,132 +14003,132 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Contact streak: 10/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 13.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 10.6 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>101.3779</t>
+          <t>102.7754</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.4367</t>
+          <t>0.4748</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1985</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.3366</t>
+          <t>0.3496</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>66.99</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>38.07</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>26.26</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.1992</t>
+          <t>0.179</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.4314</t>
+          <t>0.3802</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -14139,22 +14139,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14164,31 +14164,31 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Delayed</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Connor Prielipp</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>687570</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>55.6</v>
+        <v>55.9</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -14202,26 +14202,26 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="Q50" t="n">
-        <v>42.3</v>
+        <v>44.2</v>
       </c>
       <c r="R50" t="n">
-        <v>37.6</v>
+        <v>57.1</v>
       </c>
       <c r="S50" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T50" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>61.5</v>
+        <v>60.3</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -14256,7 +14256,7 @@
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -14273,142 +14273,142 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>51.13</t>
+          <t>42.76</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>103.2722</t>
+          <t>101.3779</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.4696</t>
+          <t>0.4367</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.2195</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3624</t>
+          <t>0.3366</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>76.71</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.2088</t>
+          <t>0.1992</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4314</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -25417,7 +25417,7 @@
         <v>50</v>
       </c>
       <c r="U90" t="n">
-        <v>24.9</v>
+        <v>23.4</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
@@ -25488,7 +25488,7 @@
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
@@ -30923,24 +30923,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>677649</t>
+          <t>691723</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Coby Mayo</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>BAL</t>
-        </is>
-      </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>2026-08-09T18:35:00Z</t>
@@ -30953,59 +30953,59 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Cade Povich</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>700249</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L110" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Strong Barrel</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
         <v>49.1</v>
       </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P110" t="n">
-        <v>20.1</v>
-      </c>
       <c r="Q110" t="n">
-        <v>52.4</v>
+        <v>45.8</v>
       </c>
       <c r="R110" t="n">
         <v>42.1</v>
       </c>
       <c r="S110" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T110" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U110" t="n">
-        <v>61.7</v>
+        <v>44.5</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
@@ -31057,12 +31057,12 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -31072,12 +31072,12 @@
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Contact streak: 9/22 over last 7 games</t>
+          <t>Last 7 games: 5/17, 1 HR</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
@@ -31087,97 +31087,97 @@
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>87.61</t>
+          <t>91.01</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>98.7042</t>
+          <t>102.9087</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.4015</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.1887</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>0.2897</t>
+          <t>0.2995</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>24.17</t>
+          <t>54.18</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>20.81</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.2053</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>91.27</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD110" t="inlineStr">
         <is>
-          <t>0.4516</t>
+          <t>0.4374</t>
         </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
-          <t>0.1861</t>
+          <t>0.1738</t>
         </is>
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="BG110" t="inlineStr">
@@ -31203,24 +31203,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>691723</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Coby Mayo</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F111" t="inlineStr">
         <is>
           <t>2026-08-09T18:35:00Z</t>
@@ -31233,26 +31233,26 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Cade Povich</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>700249</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
@@ -31266,26 +31266,26 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>49.1</v>
+        <v>20.1</v>
       </c>
       <c r="Q111" t="n">
-        <v>45.8</v>
+        <v>52.4</v>
       </c>
       <c r="R111" t="n">
         <v>42.1</v>
       </c>
       <c r="S111" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T111" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U111" t="n">
-        <v>37.8</v>
+        <v>61.7</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
@@ -31337,12 +31337,12 @@
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -31352,12 +31352,12 @@
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/16, 1 HR</t>
+          <t>Contact streak: 9/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
@@ -31367,97 +31367,97 @@
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>91.01</t>
+          <t>87.61</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>102.9087</t>
+          <t>98.7042</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
         <is>
-          <t>0.4015</t>
+          <t>0.358</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>0.1887</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>0.2995</t>
+          <t>0.2897</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>54.18</t>
+          <t>24.17</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>20.81</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>0.2053</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>91.27</t>
         </is>
       </c>
       <c r="BD111" t="inlineStr">
         <is>
-          <t>0.4374</t>
+          <t>0.4516</t>
         </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
-          <t>0.1738</t>
+          <t>0.1861</t>
         </is>
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="BG111" t="inlineStr">
@@ -32125,7 +32125,7 @@
         <v>80</v>
       </c>
       <c r="U114" t="n">
-        <v>16.6</v>
+        <v>15.3</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -32192,7 +32192,7 @@
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
@@ -34279,24 +34279,24 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>701675</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>STL</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
       <c r="F122" t="inlineStr">
         <is>
           <t>2026-08-09T18:15:00Z</t>
@@ -34309,17 +34309,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -34342,26 +34342,26 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>17.9</v>
+        <v>23.6</v>
       </c>
       <c r="Q122" t="n">
-        <v>54.4</v>
+        <v>56.2</v>
       </c>
       <c r="R122" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="S122" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T122" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U122" t="n">
-        <v>54.9</v>
+        <v>27.7</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -34413,27 +34413,27 @@
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 7/23, 0 HR</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
@@ -34443,57 +34443,57 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>87.04</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>98.1508</t>
+          <t>99.6358</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>0.3427</t>
+          <t>0.3572</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>0.1137</t>
+          <t>0.1159</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>0.2785</t>
+          <t>0.3147</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>69.67</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>35.55</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -34503,37 +34503,37 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>0.1102</t>
+          <t>0.1238</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>90.56</t>
+          <t>90.43</t>
         </is>
       </c>
       <c r="BD122" t="inlineStr">
         <is>
-          <t>0.4713</t>
+          <t>0.4857</t>
         </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
-          <t>0.1847</t>
+          <t>0.2019</t>
         </is>
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>26.06</t>
         </is>
       </c>
       <c r="BG122" t="inlineStr">
@@ -34839,27 +34839,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>694208</t>
+          <t>701675</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Moisés Ballesteros</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-09T17:40:00Z</t>
+          <t>2026-08-09T18:15:00Z</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -34869,17 +34869,17 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -34888,7 +34888,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
@@ -34906,22 +34906,22 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>35.8</v>
+        <v>17.9</v>
       </c>
       <c r="Q124" t="n">
-        <v>47.3</v>
+        <v>54.4</v>
       </c>
       <c r="R124" t="n">
-        <v>35</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S124" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T124" t="n">
         <v>80</v>
       </c>
       <c r="U124" t="n">
-        <v>3.4</v>
+        <v>52.5</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -34973,27 +34973,27 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 8.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.4 HR allowed</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -35003,112 +35003,112 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>43.17</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>90.01</t>
+          <t>87.04</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>101.0295</t>
+          <t>98.1508</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>0.3986</t>
+          <t>0.3427</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>0.1506</t>
+          <t>0.1137</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>0.3193</t>
+          <t>0.2785</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>8.41</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.55</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>0.1494</t>
+          <t>0.1102</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.56</t>
         </is>
       </c>
       <c r="BD124" t="inlineStr">
         <is>
-          <t>0.4264</t>
+          <t>0.4713</t>
         </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.1847</t>
         </is>
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI124" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ124" t="inlineStr"/>
@@ -35119,27 +35119,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>681297</t>
+          <t>694208</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Colton Cowser</t>
+          <t>Moisés Ballesteros</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-09T18:35:00Z</t>
+          <t>2026-08-09T17:40:00Z</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -35149,17 +35149,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -35182,26 +35182,26 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>42.5</v>
+        <v>35.8</v>
       </c>
       <c r="Q125" t="n">
-        <v>45.8</v>
+        <v>47.3</v>
       </c>
       <c r="R125" t="n">
-        <v>42.1</v>
+        <v>35</v>
       </c>
       <c r="S125" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T125" t="n">
         <v>80</v>
       </c>
       <c r="U125" t="n">
-        <v>40.3</v>
+        <v>3.4</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -35253,27 +35253,27 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 1 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 8.6 HR allowed</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
@@ -35283,97 +35283,97 @@
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>11.44</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>90.01</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>100.3483</t>
+          <t>101.0295</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>0.3998</t>
+          <t>0.3986</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>0.1946</t>
+          <t>0.1506</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>0.3077</t>
+          <t>0.3193</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>74.37</t>
+          <t>72.92</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1494</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>45.77</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>0.4374</t>
+          <t>0.4264</t>
         </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
-          <t>0.1738</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr">
@@ -35383,12 +35383,12 @@
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI125" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ125" t="inlineStr"/>
@@ -35399,27 +35399,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>596142</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Gary Sánchez</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-09T18:15:00Z</t>
+          <t>2026-08-09T18:10:00Z</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -35429,22 +35429,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Connor Prielipp</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>687570</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -35462,26 +35462,26 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>23.6</v>
+        <v>42.7</v>
       </c>
       <c r="Q126" t="n">
-        <v>56.2</v>
+        <v>42.3</v>
       </c>
       <c r="R126" t="n">
-        <v>68.09999999999999</v>
+        <v>37.6</v>
       </c>
       <c r="S126" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T126" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U126" t="n">
-        <v>22.9</v>
+        <v>37.8</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -35516,7 +35516,7 @@
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr"/>
@@ -35533,27 +35533,27 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 4/16, 1 HR</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
@@ -35563,112 +35563,112 @@
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>99.6358</t>
+          <t>101.0402</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>0.3572</t>
+          <t>0.435</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>0.1159</t>
+          <t>0.2013</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>0.3147</t>
+          <t>0.3493</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>71.99</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>0.1238</t>
+          <t>0.2122</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>90.43</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>0.4857</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
-          <t>0.2019</t>
+          <t>0.159</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI126" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ126" t="inlineStr"/>
@@ -35679,27 +35679,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>682626</t>
+          <t>681297</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Francisco Alvarez</t>
+          <t>Colton Cowser</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-09T17:35:00Z</t>
+          <t>2026-08-09T18:35:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -35709,17 +35709,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -35728,7 +35728,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
@@ -35742,26 +35742,26 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>56.3</v>
+        <v>42.5</v>
       </c>
       <c r="Q127" t="n">
-        <v>38.8</v>
+        <v>45.8</v>
       </c>
       <c r="R127" t="n">
-        <v>49.3</v>
+        <v>42.1</v>
       </c>
       <c r="S127" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T127" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U127" t="n">
-        <v>32.9</v>
+        <v>37.8</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -35796,7 +35796,7 @@
       <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr"/>
@@ -35813,12 +35813,12 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
@@ -35828,12 +35828,12 @@
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 1 HR</t>
+          <t>Last 7 games: 4/16, 1 HR</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
@@ -35843,112 +35843,112 @@
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>11.44</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>47.02</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>90.93</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>102.7112</t>
+          <t>100.3483</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.4545</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>0.1946</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.3386</t>
+          <t>0.3077</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>74.37</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1819</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>0.4374</t>
         </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1738</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH127" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr"/>
@@ -35959,12 +35959,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>666182</t>
+          <t>682626</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bo Bichette</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -35989,7 +35989,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -36008,7 +36008,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -36022,11 +36022,11 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>31.3</v>
+        <v>56.3</v>
       </c>
       <c r="Q128" t="n">
         <v>38.8</v>
@@ -36035,13 +36035,13 @@
         <v>49.3</v>
       </c>
       <c r="S128" t="n">
-        <v>96.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="T128" t="n">
         <v>50</v>
       </c>
       <c r="U128" t="n">
-        <v>48.5</v>
+        <v>32.9</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -36093,12 +36093,12 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Contact streak: 9/28 over last 7 games</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
@@ -36123,67 +36123,67 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>15.32</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>47.02</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>90.93</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>100.9759</t>
+          <t>102.7112</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>0.4254</t>
+          <t>0.4545</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>0.1447</t>
+          <t>0.215</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>0.3278</t>
+          <t>0.3386</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>74.11</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>13.23</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>26.84</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.1819</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
@@ -36239,27 +36239,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>642350</t>
+          <t>666182</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jose Siri</t>
+          <t>Bo Bichette</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-09T17:40:00Z</t>
+          <t>2026-08-09T17:35:00Z</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -36269,17 +36269,17 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -36288,7 +36288,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -36302,26 +36302,26 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>45.1</v>
+        <v>31.3</v>
       </c>
       <c r="Q129" t="n">
-        <v>47.3</v>
+        <v>38.8</v>
       </c>
       <c r="R129" t="n">
-        <v>35</v>
+        <v>49.3</v>
       </c>
       <c r="S129" t="n">
-        <v>52.4</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T129" t="n">
         <v>50</v>
       </c>
       <c r="U129" t="n">
-        <v>81.2</v>
+        <v>48.5</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -36356,7 +36356,7 @@
       <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr"/>
@@ -36373,142 +36373,142 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 8.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>14.61</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>99.4466</t>
+          <t>100.9759</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.4254</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.1861</t>
+          <t>0.1447</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.2813</t>
+          <t>0.3278</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>73.29</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>26.84</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.4264</t>
+          <t>0.377</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Calm</t>
         </is>
       </c>
       <c r="BH129" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI129" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ129" t="inlineStr"/>
@@ -36519,27 +36519,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>642350</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Gary Sánchez</t>
+          <t>Jose Siri</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-09T18:10:00Z</t>
+          <t>2026-08-09T17:40:00Z</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -36549,22 +36549,22 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Connor Prielipp</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>687570</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -36582,26 +36582,26 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>42.7</v>
+        <v>45.1</v>
       </c>
       <c r="Q130" t="n">
-        <v>42.3</v>
+        <v>47.3</v>
       </c>
       <c r="R130" t="n">
-        <v>37.6</v>
+        <v>35</v>
       </c>
       <c r="S130" t="n">
-        <v>64.3</v>
+        <v>52.4</v>
       </c>
       <c r="T130" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U130" t="n">
-        <v>30.3</v>
+        <v>81.2</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -36636,7 +36636,7 @@
       <c r="AB130" t="inlineStr"/>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr"/>
@@ -36653,142 +36653,142 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 8.6 HR allowed</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>14.61</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>101.0402</t>
+          <t>99.4466</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>0.2013</t>
+          <t>0.1861</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>0.3493</t>
+          <t>0.2813</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>71.99</t>
+          <t>73.29</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>0.2122</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>45.77</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4264</t>
         </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH130" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI130" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ130" t="inlineStr"/>
@@ -37915,52 +37915,52 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>687637</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-09T18:35:00Z</t>
+          <t>2026-08-09T20:10:00Z</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Eduardo Rodriguez</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>593958</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L135" t="n">
@@ -37978,26 +37978,26 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P135" t="n">
-        <v>29.5</v>
+        <v>34.9</v>
       </c>
       <c r="Q135" t="n">
-        <v>45.8</v>
+        <v>43.4</v>
       </c>
       <c r="R135" t="n">
-        <v>42.1</v>
+        <v>41.7</v>
       </c>
       <c r="S135" t="n">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T135" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U135" t="n">
-        <v>15.3</v>
+        <v>75.8</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -38011,7 +38011,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -38049,27 +38049,27 @@
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 16.6 HR allowed</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
@@ -38079,97 +38079,97 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>99.3084</t>
+          <t>98.9543</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>0.3842</t>
+          <t>0.4228</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>0.3209</t>
+          <t>0.3475</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>40.32</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>0.1191</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="BD135" t="inlineStr">
         <is>
-          <t>0.4374</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
-          <t>0.1738</t>
+          <t>0.1804</t>
         </is>
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>26.91</t>
         </is>
       </c>
       <c r="BG135" t="inlineStr">
@@ -38179,12 +38179,12 @@
       </c>
       <c r="BH135" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI135" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ135" t="inlineStr"/>
@@ -38195,56 +38195,56 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>687637</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-09T20:10:00Z</t>
+          <t>2026-08-09T18:35:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Eduardo Rodriguez</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>593958</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -38258,26 +38258,26 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>34.9</v>
+        <v>29.5</v>
       </c>
       <c r="Q136" t="n">
-        <v>43.4</v>
+        <v>45.8</v>
       </c>
       <c r="R136" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="S136" t="n">
-        <v>76.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T136" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U136" t="n">
-        <v>75.8</v>
+        <v>13.6</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
@@ -38329,27 +38329,27 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 16.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
@@ -38359,97 +38359,97 @@
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>98.9543</t>
+          <t>99.3084</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.4228</t>
+          <t>0.3842</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.1584</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.3475</t>
+          <t>0.3209</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>40.32</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.1581</t>
+          <t>0.1191</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.4374</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.1804</t>
+          <t>0.1738</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr">
@@ -38459,12 +38459,12 @@
       </c>
       <c r="BH136" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr"/>
@@ -41040,7 +41040,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>75</v>
       </c>
       <c r="U146" t="n">
-        <v>17.7</v>
+        <v>16.1</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
@@ -41144,7 +41144,7 @@
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
@@ -41357,7 +41357,7 @@
         <v>50</v>
       </c>
       <c r="U147" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -41414,7 +41414,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
@@ -43614,7 +43614,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
@@ -43624,7 +43624,7 @@
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 1 HR</t>
+          <t>Last 7 games: 2/19, 1 HR</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
@@ -47671,27 +47671,27 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-09T17:40:00Z</t>
+          <t>2026-08-09T18:15:00Z</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -47701,17 +47701,17 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>Michael Lorenzen</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -47720,7 +47720,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
@@ -47734,26 +47734,26 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P170" t="n">
-        <v>12.7</v>
+        <v>14.4</v>
       </c>
       <c r="Q170" t="n">
-        <v>47.3</v>
+        <v>54.4</v>
       </c>
       <c r="R170" t="n">
-        <v>35</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S170" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T170" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U170" t="n">
-        <v>50.3</v>
+        <v>10.6</v>
       </c>
       <c r="V170" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y170" t="inlineStr">
@@ -47788,7 +47788,7 @@
       <c r="AB170" t="inlineStr"/>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr"/>
@@ -47805,27 +47805,27 @@
       </c>
       <c r="AH170" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL170" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 8.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.4 HR allowed</t>
         </is>
       </c>
       <c r="AM170" t="inlineStr">
@@ -47835,112 +47835,112 @@
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
         <is>
-          <t>96.4402</t>
+          <t>98.5597</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>0.0846</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>0.2972</t>
         </is>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.089</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.56</t>
         </is>
       </c>
       <c r="BD170" t="inlineStr">
         <is>
-          <t>0.4264</t>
+          <t>0.4713</t>
         </is>
       </c>
       <c r="BE170" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.1847</t>
         </is>
       </c>
       <c r="BF170" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>25.87</t>
         </is>
       </c>
       <c r="BG170" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH170" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI170" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ170" t="inlineStr"/>
@@ -47951,12 +47951,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>694384</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -47981,7 +47981,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -48018,7 +48018,7 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>14</v>
+        <v>12.7</v>
       </c>
       <c r="Q171" t="n">
         <v>47.3</v>
@@ -48027,13 +48027,13 @@
         <v>35</v>
       </c>
       <c r="S171" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T171" t="n">
         <v>80</v>
       </c>
       <c r="U171" t="n">
-        <v>32.9</v>
+        <v>50.3</v>
       </c>
       <c r="V171" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y171" t="inlineStr">
@@ -48068,7 +48068,7 @@
       <c r="AB171" t="inlineStr"/>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD171" t="inlineStr"/>
@@ -48085,12 +48085,12 @@
       </c>
       <c r="AH171" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ171" t="inlineStr">
@@ -48100,7 +48100,7 @@
       </c>
       <c r="AK171" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 1 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL171" t="inlineStr">
@@ -48115,67 +48115,67 @@
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>87.57</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
         <is>
-          <t>97.0841</t>
+          <t>96.4402</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.111</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr">
         <is>
-          <t>0.3291</t>
+          <t>0.318</t>
         </is>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>67.89</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>0.1194</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
@@ -48231,47 +48231,47 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>694384</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-09T20:10:00Z</t>
+          <t>2026-08-09T17:40:00Z</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Emerson Hancock</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>676106</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -48294,26 +48294,26 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P172" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q172" t="n">
-        <v>48.2</v>
+        <v>47.3</v>
       </c>
       <c r="R172" t="n">
-        <v>52.4</v>
+        <v>35</v>
       </c>
       <c r="S172" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T172" t="n">
         <v>80</v>
       </c>
       <c r="U172" t="n">
-        <v>39.5</v>
+        <v>32.9</v>
       </c>
       <c r="V172" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
@@ -48365,7 +48365,7 @@
       </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI172" t="inlineStr">
@@ -48380,12 +48380,12 @@
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 8.6 HR allowed</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
@@ -48395,112 +48395,112 @@
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>85.02</t>
+          <t>87.57</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>96.3149</t>
+          <t>97.0841</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>0.3493</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>0.1011</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>0.3136</t>
+          <t>0.3291</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>67.89</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>0.1389</t>
+          <t>0.1194</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>45.77</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="BD172" t="inlineStr">
         <is>
-          <t>0.4358</t>
+          <t>0.4264</t>
         </is>
       </c>
       <c r="BE172" t="inlineStr">
         <is>
-          <t>0.1759</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="BG172" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH172" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI172" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ172" t="inlineStr"/>
@@ -48511,47 +48511,47 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-09T18:15:00Z</t>
+          <t>2026-08-09T20:10:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Michael Lorenzen</t>
+          <t>Emerson Hancock</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>547179</t>
+          <t>676106</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -48560,7 +48560,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -48574,26 +48574,26 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>14.4</v>
+        <v>9</v>
       </c>
       <c r="Q173" t="n">
-        <v>54.4</v>
+        <v>48.2</v>
       </c>
       <c r="R173" t="n">
-        <v>68.09999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="S173" t="n">
-        <v>76.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T173" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U173" t="n">
-        <v>4.5</v>
+        <v>39.5</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -48645,27 +48645,27 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 19.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -48675,112 +48675,112 @@
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>85.02</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>98.5597</t>
+          <t>96.3149</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.3493</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>0.0846</t>
+          <t>0.1011</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.2972</t>
+          <t>0.3136</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>0.1389</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>42.78</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>90.56</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>0.4713</t>
+          <t>0.4358</t>
         </is>
       </c>
       <c r="BE173" t="inlineStr">
         <is>
-          <t>0.1847</t>
+          <t>0.1759</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="BG173" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH173" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr"/>
@@ -51316,7 +51316,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
@@ -51349,7 +51349,7 @@
         <v>75</v>
       </c>
       <c r="U183" t="n">
-        <v>43.2</v>
+        <v>40.3</v>
       </c>
       <c r="V183" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ183" t="inlineStr">
@@ -51416,7 +51416,7 @@
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/14, 1 HR</t>
+          <t>Last 7 games: 4/15, 1 HR</t>
         </is>
       </c>
       <c r="AL183" t="inlineStr">
@@ -53107,52 +53107,52 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>543760</t>
+          <t>814439</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Ryan Waldschmidt</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-08-09T17:35:00Z</t>
+          <t>2026-08-09T20:10:00Z</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L190" t="n">
@@ -53170,50 +53170,42 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P190" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q190" t="n">
-        <v>38.8</v>
+        <v>45.2</v>
       </c>
       <c r="R190" t="n">
-        <v>49.3</v>
+        <v>41.7</v>
       </c>
       <c r="S190" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T190" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U190" t="n">
-        <v>59.6</v>
+        <v>44.1</v>
       </c>
       <c r="V190" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="W190" t="inlineStr"/>
+      <c r="X190" t="inlineStr"/>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -53221,10 +53213,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB190" t="inlineStr"/>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr"/>
@@ -53241,27 +53237,27 @@
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL190" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM190" t="inlineStr">
@@ -53271,112 +53267,112 @@
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>87.18</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
         <is>
-          <t>97.7436</t>
+          <t>98.8213</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
         <is>
-          <t>0.3992</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>0.1537</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>0.1459</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="BD190" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="BE190" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="BF190" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="BG190" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH190" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI190" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ190" t="inlineStr"/>
@@ -53387,56 +53383,56 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>814439</t>
+          <t>543760</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Ryan Waldschmidt</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-08-09T20:10:00Z</t>
+          <t>2026-08-09T17:35:00Z</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Justin Wrobleski</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>680736</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
@@ -53450,57 +53446,61 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P191" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q191" t="n">
-        <v>45.2</v>
+        <v>38.8</v>
       </c>
       <c r="R191" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="S191" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T191" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U191" t="n">
-        <v>44.1</v>
+        <v>57.8</v>
       </c>
       <c r="V191" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W191" t="inlineStr"/>
-      <c r="X191" t="inlineStr"/>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y191" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB191" t="inlineStr"/>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr"/>
@@ -53517,27 +53517,27 @@
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL191" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 13.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
@@ -53547,112 +53547,112 @@
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.18</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
         <is>
-          <t>98.8213</t>
+          <t>97.7436</t>
         </is>
       </c>
       <c r="AR191" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>0.3992</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1537</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>68.57</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>32.07</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1459</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD191" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.377</t>
         </is>
       </c>
       <c r="BE191" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="BG191" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Calm</t>
         </is>
       </c>
       <c r="BH191" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI191" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ191" t="inlineStr"/>
@@ -54922,7 +54922,7 @@
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AJ196" t="inlineStr">
@@ -54932,7 +54932,7 @@
       </c>
       <c r="AK196" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/5, 0 HR</t>
+          <t>Last 7 games: 0/6, 0 HR</t>
         </is>
       </c>
       <c r="AL196" t="inlineStr">
@@ -56784,7 +56784,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
@@ -56817,7 +56817,7 @@
         <v>50</v>
       </c>
       <c r="U203" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="V203" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ203" t="inlineStr">
@@ -56884,7 +56884,7 @@
       </c>
       <c r="AK203" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 1 HR</t>
+          <t>Last 7 games: 3/24, 1 HR</t>
         </is>
       </c>
       <c r="AL203" t="inlineStr">
@@ -58180,7 +58180,7 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         <v>75</v>
       </c>
       <c r="U208" t="n">
-        <v>10.1</v>
+        <v>8.5</v>
       </c>
       <c r="V208" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ208" t="inlineStr">
@@ -58280,7 +58280,7 @@
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 3/17, 0 HR</t>
         </is>
       </c>
       <c r="AL208" t="inlineStr">
@@ -58971,47 +58971,47 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>642215</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-08-09T17:35:00Z</t>
+          <t>2026-08-09T20:10:00Z</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Erik Miller</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>669062</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -59034,26 +59034,26 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P211" t="n">
-        <v>38</v>
+        <v>19.8</v>
       </c>
       <c r="Q211" t="n">
-        <v>9.199999999999999</v>
+        <v>40.5</v>
       </c>
       <c r="R211" t="n">
-        <v>69.7</v>
+        <v>52.4</v>
       </c>
       <c r="S211" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T211" t="n">
         <v>78</v>
       </c>
       <c r="U211" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="V211" t="inlineStr">
         <is>
@@ -59077,7 +59077,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -59085,11 +59085,7 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB211" t="inlineStr"/>
       <c r="AC211" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -59109,12 +59105,12 @@
       </c>
       <c r="AH211" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI211" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ211" t="inlineStr">
@@ -59124,112 +59120,112 @@
       </c>
       <c r="AK211" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 0 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL211" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 1.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 10.6 HR allowed</t>
         </is>
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>86.32</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>101.3649</t>
+          <t>97.786</t>
         </is>
       </c>
       <c r="AR211" t="inlineStr">
         <is>
-          <t>0.3544</t>
+          <t>0.3171</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>0.1465</t>
+          <t>0.1179</t>
         </is>
       </c>
       <c r="AT211" t="inlineStr">
         <is>
-          <t>0.2782</t>
+          <t>0.2691</t>
         </is>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>74.01</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>27.52</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>47.69</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>0.1573</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>84.65</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="BD211" t="inlineStr">
         <is>
-          <t>0.3043</t>
+          <t>0.3802</t>
         </is>
       </c>
       <c r="BE211" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF211" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="BG211" t="inlineStr">
@@ -59239,12 +59235,12 @@
       </c>
       <c r="BH211" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BI211" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ211" t="inlineStr"/>
@@ -59255,47 +59251,47 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>642215</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Weston Wilson</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-08-09T20:10:00Z</t>
+          <t>2026-08-09T17:35:00Z</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Erik Miller</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>669062</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -59304,7 +59300,7 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
@@ -59318,26 +59314,26 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P212" t="n">
-        <v>19.8</v>
+        <v>38</v>
       </c>
       <c r="Q212" t="n">
-        <v>40.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R212" t="n">
-        <v>52.4</v>
+        <v>69.7</v>
       </c>
       <c r="S212" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T212" t="n">
         <v>78</v>
       </c>
       <c r="U212" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="V212" t="inlineStr">
         <is>
@@ -59361,7 +59357,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -59369,7 +59365,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>order MLB 9 vs RotoWire 8</t>
+        </is>
+      </c>
       <c r="AC212" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -59389,12 +59389,12 @@
       </c>
       <c r="AH212" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ212" t="inlineStr">
@@ -59404,112 +59404,112 @@
       </c>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL212" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 10.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 1.4 HR allowed</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>86.32</t>
+          <t>89.62</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>97.786</t>
+          <t>101.3649</t>
         </is>
       </c>
       <c r="AR212" t="inlineStr">
         <is>
-          <t>0.3171</t>
+          <t>0.3544</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>0.1179</t>
+          <t>0.1465</t>
         </is>
       </c>
       <c r="AT212" t="inlineStr">
         <is>
-          <t>0.2691</t>
+          <t>0.2782</t>
         </is>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>72.71</t>
+          <t>74.01</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>45.12</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>47.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>24.33</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1573</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>28.86</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>84.65</t>
         </is>
       </c>
       <c r="BD212" t="inlineStr">
         <is>
-          <t>0.3802</t>
+          <t>0.3043</t>
         </is>
       </c>
       <c r="BE212" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.101</t>
         </is>
       </c>
       <c r="BF212" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BG212" t="inlineStr">
@@ -59519,12 +59519,12 @@
       </c>
       <c r="BH212" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI212" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ212" t="inlineStr"/>
@@ -61504,7 +61504,7 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
@@ -61537,7 +61537,7 @@
         <v>50</v>
       </c>
       <c r="U220" t="n">
-        <v>10.1</v>
+        <v>8.5</v>
       </c>
       <c r="V220" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ220" t="inlineStr">
@@ -61604,7 +61604,7 @@
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 3/17, 0 HR</t>
         </is>
       </c>
       <c r="AL220" t="inlineStr">
@@ -63514,7 +63514,7 @@
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
@@ -63524,7 +63524,7 @@
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Contact streak: 6/13 over last 7 games</t>
+          <t>Contact streak: 6/14 over last 7 games</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
@@ -65426,7 +65426,7 @@
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
@@ -65436,7 +65436,7 @@
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/9, 0 HR</t>
+          <t>Last 7 games: 1/10, 0 HR</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
@@ -73304,7 +73304,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -73314,7 +73314,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Last 7 games: 2/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -74894,7 +74894,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -74927,7 +74927,7 @@
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>56.2</v>
+        <v>54.4</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -74984,7 +74984,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
